--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-administration-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-medication-administration-document.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,10 +85,9 @@
   </si>
   <si>
     <t xml:space="preserve">
- - L'entrée 'Traitement' est une entrée de type 'substanceAdministration' décrivant les modalités d'administration d'un médicament au patient.
- - Elle permet de décrire notamment le médicament, le mode d'administration, la quantité, la durée et la fréquence d'administration.
- - Si le traitement est en attente d’administration (c’est-à dire qu’il a été prescrit) : 
-  • @moodCode='INT'</t>
+ - FrMedicationAdministrationDocument permert de décrire les modalités d'administration d'un médicament au patient.
+ - Il permet de décrire notamment le médicament, le mode d'administration, la quantité, la durée et la fréquence d'administration.
+ - Si le traitement est en attente d’administration c’est-à dire qu’il a été prescrit.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -388,7 +387,7 @@
 </t>
   </si>
   <si>
-    <t>Partie narrative de l’entrée</t>
+    <t>Partie narrative</t>
   </si>
   <si>
     <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
@@ -466,10 +465,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Prescription</t>
-  </si>
-  <si>
-    <t>Instructions de prescription associées à l'administration du produit de santé.</t>
+    <t>Extension - Fr Prescription</t>
+  </si>
+  <si>
+    <t>Extension permettant d’indiquer les instructions de prescription associées à l'administration du produit de santé.</t>
   </si>
   <si>
     <t xml:space="preserve">ele-1
@@ -486,10 +485,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Précondition de l'administration</t>
-  </si>
-  <si>
-    <t>Lien vers la description narrative des conditions préalables dans le document CDA.</t>
+    <t>Extension - Fr Précondition de l'administration</t>
+  </si>
+  <si>
+    <t>Extension permettant d'indiquer le lien vers la description narrative des conditions préalables dans le document.</t>
   </si>
   <si>
     <t>MedicationAdministration.modifierExtension</t>
@@ -522,7 +521,7 @@
 </t>
   </si>
   <si>
-    <t>Identifiant de l'entrée. L'entrée Traitement doit être identifiée de manière unique.</t>
+    <t>Identifiant. L'entrée Traitement doit être identifiée de manière unique.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Administration that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -577,7 +576,7 @@
     <t>MedicationAdministration.status</t>
   </si>
   <si>
-    <t>Statut de l’entrée</t>
+    <t>Statut</t>
   </si>
   <si>
     <t>Will generally be set to show that the administration has been completed.  For some long running administrations such as infusions, it is possible for an administration to be started but not completed or it may be paused while some other process is under way.</t>
@@ -921,7 +920,7 @@
     <t>MedicationAdministration.reasonReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Condition|Observation)
+    <t xml:space="preserve">Reference(https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-condition|Observation)
 </t>
   </si>
   <si>
@@ -1044,7 +1043,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Fréquence d’administration</t>
+    <t>Extension - Fr Fréquence d’administration</t>
   </si>
   <si>
     <t>Extension pour représenter la fréquence d'administration dans MedicationAdministration et MedicationStatement</t>
@@ -1060,10 +1059,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Sequence</t>
-  </si>
-  <si>
-    <t>Dosages progressifs et fractionnés</t>
+    <t>Extension - Fr Sequence</t>
+  </si>
+  <si>
+    <t>Extension utilisée dans le contexte de MedicationAdministration pour indiquer l’ordre d’une prise dans le cadre d’un schéma de traitement comportant des dosages progressifs ou fractionnés. La valeur est un entier (integer) représentant le numéro de séquence de l’administration.</t>
   </si>
   <si>
     <t>MedicationAdministration.dosage.modifierExtension</t>
